--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487001_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487001_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.1967</v>
+        <v>2.448</v>
       </c>
       <c r="E2" t="n">
-        <v>2.5124</v>
+        <v>1.9119</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6843</v>
+        <v>0.5361</v>
       </c>
       <c r="G2" t="n">
         <v>0.415</v>
@@ -610,13 +610,13 @@
         <v>2.0534</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5249</v>
+        <v>-0.2237</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6583</v>
+        <v>0.0579</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1334</v>
+        <v>-0.2816</v>
       </c>
       <c r="V2" t="n">
         <v>2.2567</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3361</v>
+        <v>0.8953</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.08</v>
+        <v>-0.4911</v>
       </c>
       <c r="F3" t="n">
-        <v>1.416</v>
+        <v>1.3864</v>
       </c>
       <c r="G3" t="n">
         <v>-0.6798999999999999</v>
@@ -688,13 +688,13 @@
         <v>1.2321</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.3331</v>
+        <v>-0.7739</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9726</v>
+        <v>-0.3837</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3605</v>
+        <v>-0.3902</v>
       </c>
       <c r="V3" t="n">
         <v>1.1171</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1822</v>
+        <v>-0.669</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0668</v>
+        <v>0.6097</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.249</v>
+        <v>-1.2787</v>
       </c>
       <c r="G4" t="n">
         <v>2.3683</v>
@@ -766,13 +766,13 @@
         <v>1.2321</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4064</v>
+        <v>-0.0804</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4221</v>
+        <v>-0.0351</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0157</v>
+        <v>-0.0453</v>
       </c>
       <c r="V4" t="n">
         <v>-1.1088</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.8063</v>
+        <v>-1.5172</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.4966</v>
+        <v>-0.3261</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.3097</v>
+        <v>-1.1911</v>
       </c>
       <c r="G5" t="n">
         <v>-1.2111</v>
@@ -844,13 +844,13 @@
         <v>0.2053</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8005</v>
+        <v>-0.5114</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4611</v>
+        <v>-0.2906</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3394</v>
+        <v>-0.2208</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-3.4913</v>
+        <v>-3.045</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.5472</v>
+        <v>-1.338</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.9441</v>
+        <v>-1.707</v>
       </c>
       <c r="G6" t="n">
         <v>-4.1733</v>
@@ -922,13 +922,13 @@
         <v>0.616</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.1825</v>
+        <v>-0.7362</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.9881</v>
+        <v>-0.7789</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1944</v>
+        <v>0.0427</v>
       </c>
       <c r="V6" t="n">
         <v>1.2484</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.9236</v>
+        <v>-4.2448</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.2061</v>
+        <v>-2.3495</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.7175</v>
+        <v>-1.8953</v>
       </c>
       <c r="G7" t="n">
         <v>-3.2239</v>
@@ -1000,13 +1000,13 @@
         <v>0.8214</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3239</v>
+        <v>-0.6451</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3566</v>
+        <v>-0.4999</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0327</v>
+        <v>-0.1452</v>
       </c>
       <c r="V7" t="n">
         <v>-0.1704</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-5.1441</v>
+        <v>-4.7628</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.3611</v>
+        <v>-3.7722</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.783</v>
+        <v>-0.9905</v>
       </c>
       <c r="G8" t="n">
         <v>-4.4179</v>
@@ -1078,13 +1078,13 @@
         <v>1.2321</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.3936</v>
+        <v>-1.0122</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.2438</v>
+        <v>-0.655</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1497</v>
+        <v>-0.3572</v>
       </c>
       <c r="V8" t="n">
         <v>1.4887</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-6.1218</v>
+        <v>-5.9827</v>
       </c>
       <c r="E9" t="n">
-        <v>-5.4319</v>
+        <v>-5.4706</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6899</v>
+        <v>-0.512</v>
       </c>
       <c r="G9" t="n">
         <v>-4.9351</v>
@@ -1156,13 +1156,13 @@
         <v>1.8481</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.6405</v>
+        <v>-1.5013</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.8487</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.8305</v>
+        <v>-0.6526</v>
       </c>
       <c r="V9" t="n">
         <v>0.6591</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-7.4236</v>
+        <v>-7.0234</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.5072</v>
+        <v>-5.1663</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.9163</v>
+        <v>-1.8571</v>
       </c>
       <c r="G10" t="n">
         <v>-6.3737</v>
@@ -1234,13 +1234,13 @@
         <v>2.0534</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0376</v>
+        <v>-0.6374</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8022</v>
+        <v>-0.4613</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2354</v>
+        <v>-0.1761</v>
       </c>
       <c r="V10" t="n">
         <v>-1.039</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-24.5601</v>
+        <v>-23.9016</v>
       </c>
       <c r="E11" t="n">
-        <v>-17.0509</v>
+        <v>-16.3922</v>
       </c>
       <c r="F11" t="n">
         <v>-7.5092</v>
@@ -1312,10 +1312,10 @@
         <v>11.2939</v>
       </c>
       <c r="S11" t="n">
-        <v>-6.7804</v>
+        <v>-6.121599999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-4.554</v>
+        <v>-3.8953</v>
       </c>
       <c r="U11" t="n">
         <v>-2.2263</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>6.3776</v>
+        <v>6.6564</v>
       </c>
       <c r="E12" t="n">
-        <v>0.8719</v>
+        <v>1.6041</v>
       </c>
       <c r="F12" t="n">
-        <v>5.5057</v>
+        <v>5.0523</v>
       </c>
       <c r="G12" t="n">
         <v>5.2655</v>
@@ -1390,13 +1390,13 @@
         <v>1.8481</v>
       </c>
       <c r="S12" t="n">
-        <v>1.5228</v>
+        <v>1.8016</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6046</v>
+        <v>0.1276</v>
       </c>
       <c r="U12" t="n">
-        <v>2.1274</v>
+        <v>1.674</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Y. KOLO</t>
+          <t>A. ARAGONES NAVAIS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.7595</v>
+        <v>6.0164</v>
       </c>
       <c r="E13" t="n">
-        <v>2.1073</v>
+        <v>2.851</v>
       </c>
       <c r="F13" t="n">
-        <v>2.6522</v>
+        <v>3.1653</v>
       </c>
       <c r="G13" t="n">
-        <v>2.0249</v>
+        <v>4.9954</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.4116</v>
+        <v>2.2773</v>
       </c>
       <c r="I13" t="n">
-        <v>2.4365</v>
+        <v>2.7181</v>
       </c>
       <c r="J13" t="n">
-        <v>1.3055</v>
+        <v>4.2576</v>
       </c>
       <c r="K13" t="n">
-        <v>0.056</v>
+        <v>1.7977</v>
       </c>
       <c r="L13" t="n">
-        <v>1.2495</v>
+        <v>2.4599</v>
       </c>
       <c r="M13" t="n">
-        <v>0.7194</v>
+        <v>0.7378</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.4676</v>
+        <v>0.4796</v>
       </c>
       <c r="O13" t="n">
-        <v>1.187</v>
+        <v>0.2582</v>
       </c>
       <c r="P13" t="n">
-        <v>0.2053</v>
+        <v>0.4107</v>
       </c>
       <c r="Q13" t="n">
         <v>-1.4374</v>
       </c>
       <c r="R13" t="n">
-        <v>1.6427</v>
+        <v>1.8481</v>
       </c>
       <c r="S13" t="n">
-        <v>3.4676</v>
+        <v>0.6102</v>
       </c>
       <c r="T13" t="n">
-        <v>1.9989</v>
+        <v>0.0308</v>
       </c>
       <c r="U13" t="n">
-        <v>1.4687</v>
+        <v>0.5794</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.9384</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.1786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. ARAGONES NAVAIS</t>
+          <t>J. ZHAO OLMOS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.4089</v>
+        <v>5.7956</v>
       </c>
       <c r="E14" t="n">
-        <v>1.7004</v>
+        <v>2.926</v>
       </c>
       <c r="F14" t="n">
-        <v>2.7085</v>
+        <v>2.8697</v>
       </c>
       <c r="G14" t="n">
-        <v>4.9954</v>
+        <v>2.8446</v>
       </c>
       <c r="H14" t="n">
-        <v>2.2773</v>
+        <v>0.5162</v>
       </c>
       <c r="I14" t="n">
-        <v>2.7181</v>
+        <v>2.3285</v>
       </c>
       <c r="J14" t="n">
-        <v>4.2576</v>
+        <v>1.4302</v>
       </c>
       <c r="K14" t="n">
-        <v>1.7977</v>
+        <v>0.3125</v>
       </c>
       <c r="L14" t="n">
-        <v>2.4599</v>
+        <v>1.1177</v>
       </c>
       <c r="M14" t="n">
-        <v>0.7378</v>
+        <v>1.4144</v>
       </c>
       <c r="N14" t="n">
-        <v>0.4796</v>
+        <v>0.2037</v>
       </c>
       <c r="O14" t="n">
-        <v>0.2582</v>
+        <v>1.2108</v>
       </c>
       <c r="P14" t="n">
-        <v>0.4107</v>
+        <v>1.6427</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.4374</v>
+        <v>-0.2053</v>
       </c>
       <c r="R14" t="n">
         <v>1.8481</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.9972</v>
+        <v>0.9366</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.1198</v>
+        <v>0.1509</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1226</v>
+        <v>0.7858000000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.3716</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.5503</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.3445</v>
+        <v>5.0802</v>
       </c>
       <c r="E15" t="n">
-        <v>2.7054</v>
+        <v>3.1238</v>
       </c>
       <c r="F15" t="n">
-        <v>1.6391</v>
+        <v>1.9564</v>
       </c>
       <c r="G15" t="n">
         <v>5.8569</v>
@@ -1624,13 +1624,13 @@
         <v>1.0267</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5206</v>
+        <v>0.2151</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.527</v>
+        <v>-0.1086</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0063</v>
+        <v>0.3237</v>
       </c>
       <c r="V15" t="n">
         <v>0.2402</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. ZHAO OLMOS</t>
+          <t>Y. KOLO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.8761</v>
+        <v>3.2601</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6707</v>
+        <v>1.0613</v>
       </c>
       <c r="F16" t="n">
-        <v>2.2054</v>
+        <v>2.1989</v>
       </c>
       <c r="G16" t="n">
-        <v>2.8446</v>
+        <v>2.0249</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5162</v>
+        <v>-0.4116</v>
       </c>
       <c r="I16" t="n">
-        <v>2.3285</v>
+        <v>2.4365</v>
       </c>
       <c r="J16" t="n">
-        <v>1.4302</v>
+        <v>1.3055</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3125</v>
+        <v>0.056</v>
       </c>
       <c r="L16" t="n">
-        <v>1.1177</v>
+        <v>1.2495</v>
       </c>
       <c r="M16" t="n">
-        <v>1.4144</v>
+        <v>0.7194</v>
       </c>
       <c r="N16" t="n">
-        <v>0.2037</v>
+        <v>-0.4676</v>
       </c>
       <c r="O16" t="n">
-        <v>1.2108</v>
+        <v>1.187</v>
       </c>
       <c r="P16" t="n">
+        <v>0.2053</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-1.4374</v>
+      </c>
+      <c r="R16" t="n">
         <v>1.6427</v>
       </c>
-      <c r="Q16" t="n">
-        <v>-0.2053</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.8481</v>
-      </c>
       <c r="S16" t="n">
-        <v>-0.9829</v>
+        <v>1.9682</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.1044</v>
+        <v>0.9529</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1215</v>
+        <v>1.0153</v>
       </c>
       <c r="V16" t="n">
-        <v>0.3716</v>
+        <v>-0.9384</v>
       </c>
       <c r="W16" t="n">
-        <v>1.5503</v>
+        <v>0.2402</v>
       </c>
       <c r="X16" t="n">
         <v>-1.1786</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.8521</v>
+        <v>2.2297</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8511</v>
+        <v>0.1189</v>
       </c>
       <c r="F17" t="n">
-        <v>2.001</v>
+        <v>2.1109</v>
       </c>
       <c r="G17" t="n">
         <v>1.0897</v>
@@ -1780,13 +1780,13 @@
         <v>1.0267</v>
       </c>
       <c r="S17" t="n">
-        <v>0.9411</v>
+        <v>0.3187</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6042</v>
+        <v>-0.128</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3368</v>
+        <v>0.4467</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.4933</v>
+        <v>1.3452</v>
       </c>
       <c r="E18" t="n">
-        <v>1.3244</v>
+        <v>0.5921999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1689</v>
+        <v>0.753</v>
       </c>
       <c r="G18" t="n">
         <v>1.6318</v>
@@ -1858,13 +1858,13 @@
         <v>1.0267</v>
       </c>
       <c r="S18" t="n">
-        <v>1.2455</v>
+        <v>1.0974</v>
       </c>
       <c r="T18" t="n">
-        <v>1.6464</v>
+        <v>0.9142</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4009</v>
+        <v>0.1832</v>
       </c>
       <c r="V18" t="n">
         <v>-1.1786</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7845</v>
+        <v>-1.78</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.6963</v>
+        <v>-1.7423</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0882</v>
+        <v>-0.0377</v>
       </c>
       <c r="G19" t="n">
         <v>1.1792</v>
@@ -1936,13 +1936,13 @@
         <v>0.8214</v>
       </c>
       <c r="S19" t="n">
-        <v>2.2149</v>
+        <v>1.2194</v>
       </c>
       <c r="T19" t="n">
-        <v>1.3829</v>
+        <v>0.3369</v>
       </c>
       <c r="U19" t="n">
-        <v>0.832</v>
+        <v>0.8826000000000001</v>
       </c>
       <c r="V19" t="n">
         <v>-2.9466</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.7674</v>
+        <v>-2.6488</v>
       </c>
       <c r="E20" t="n">
         <v>-3.0257</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2583</v>
+        <v>0.3769</v>
       </c>
       <c r="G20" t="n">
         <v>-2.6566</v>
@@ -2014,13 +2014,13 @@
         <v>0.2053</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1108</v>
+        <v>0.0077</v>
       </c>
       <c r="T20" t="n">
         <v>-0.0504</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0604</v>
+        <v>0.0581</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>24.5601</v>
+        <v>25.9548</v>
       </c>
       <c r="E21" t="n">
-        <v>7.5092</v>
+        <v>7.509299999999998</v>
       </c>
       <c r="F21" t="n">
-        <v>17.0509</v>
+        <v>18.4457</v>
       </c>
       <c r="G21" t="n">
         <v>22.2314</v>
@@ -2083,7 +2083,7 @@
         <v>6.1725</v>
       </c>
       <c r="P21" t="n">
-        <v>-9.999999999976694e-05</v>
+        <v>-9.999999999998899e-05</v>
       </c>
       <c r="Q21" t="n">
         <v>-11.2938</v>
@@ -2092,13 +2092,13 @@
         <v>11.2938</v>
       </c>
       <c r="S21" t="n">
-        <v>6.7804</v>
+        <v>8.174899999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>2.2262</v>
+        <v>2.2263</v>
       </c>
       <c r="U21" t="n">
-        <v>4.554</v>
+        <v>5.9488</v>
       </c>
       <c r="V21" t="n">
         <v>-4.4518</v>
